--- a/Signature Integration Milestone View — Roper Update 2026-04-05.xlsx
+++ b/Signature Integration Milestone View — Roper Update 2026-04-05.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1319,7 +1318,7 @@
         </is>
       </c>
       <c r="I18" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -1391,7 +1390,7 @@
         </is>
       </c>
       <c r="I20" s="31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -1720,7 +1719,7 @@
         </is>
       </c>
       <c r="I33" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2123,7 +2122,7 @@
         </is>
       </c>
       <c r="I48" s="31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -2226,7 +2225,7 @@
         </is>
       </c>
       <c r="I51" s="31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2356,7 +2355,7 @@
         </is>
       </c>
       <c r="I55" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -2671,7 +2670,7 @@
         </is>
       </c>
       <c r="I66" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -2793,7 +2792,7 @@
         </is>
       </c>
       <c r="I70" s="31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71">
@@ -2815,6 +2814,8 @@
         <v>46161.70833332176</v>
       </c>
     </row>
+    <row r="72"/>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
@@ -2897,7 +2898,7 @@
         </is>
       </c>
       <c r="I76" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -2975,7 +2976,7 @@
         </is>
       </c>
       <c r="I78" s="34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -3014,7 +3015,7 @@
         </is>
       </c>
       <c r="I79" s="34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
@@ -3053,7 +3054,7 @@
         </is>
       </c>
       <c r="I80" s="34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
@@ -3092,7 +3093,7 @@
         </is>
       </c>
       <c r="I81" s="34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
@@ -3131,7 +3132,7 @@
         </is>
       </c>
       <c r="I82" s="34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -3170,7 +3171,7 @@
         </is>
       </c>
       <c r="I83" s="34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84">
@@ -3209,7 +3210,7 @@
         </is>
       </c>
       <c r="I84" s="34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
@@ -3251,6 +3252,8 @@
         <v>19</v>
       </c>
     </row>
+    <row r="86"/>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
@@ -3549,6 +3552,8 @@
       </c>
       <c r="I97" s="34" t="n"/>
     </row>
+    <row r="98"/>
+    <row r="99"/>
     <row r="100">
       <c r="A100" s="33" t="inlineStr">
         <is>

--- a/Signature Integration Milestone View — Roper Update 2026-04-05.xlsx
+++ b/Signature Integration Milestone View — Roper Update 2026-04-05.xlsx
@@ -149,7 +149,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -220,6 +220,12 @@
         <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4C6E7"/>
+        <bgColor rgb="00B4C6E7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -233,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -326,6 +332,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="24" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,7 +730,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2108,7 +2115,7 @@
       </c>
       <c r="F48" s="31" t="inlineStr">
         <is>
-          <t>Initial session 3/28 done. 3 follow-ups requested</t>
+          <t>Initial session 3/28 done. 3 follow-ups requested | Courtney follow-up 4/6: wants additional session this week</t>
         </is>
       </c>
       <c r="G48" s="31" t="inlineStr">
@@ -2126,142 +2133,140 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
+        <is>
+          <t>03. Technology</t>
+        </is>
+      </c>
+      <c r="B49" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ Application Deep Dive — Airtable</t>
+        </is>
+      </c>
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D49" s="36" t="n"/>
+      <c r="E49" s="36" t="n"/>
+      <c r="F49" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ NEW 4/6 — Courtney Kendrick requested 4/2, follow-up 4/6. Target week of 4/13. ~1 hour</t>
+        </is>
+      </c>
+      <c r="G49" s="36" t="inlineStr">
+        <is>
+          <t>Provide availability</t>
+        </is>
+      </c>
+      <c r="H49" s="36" t="inlineStr">
+        <is>
+          <t>Roper (waiting)</t>
+        </is>
+      </c>
+      <c r="I49" s="36" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="36" t="inlineStr">
+        <is>
+          <t>03. Technology</t>
+        </is>
+      </c>
+      <c r="B50" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ Application Deep Dive — Claude AI</t>
+        </is>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D50" s="36" t="n"/>
+      <c r="E50" s="36" t="n"/>
+      <c r="F50" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ NEW 4/6 — Courtney Kendrick requested 4/2, follow-up 4/6. Target week of 4/20. ~1 hour</t>
+        </is>
+      </c>
+      <c r="G50" s="36" t="inlineStr">
+        <is>
+          <t>Provide availability</t>
+        </is>
+      </c>
+      <c r="H50" s="36" t="inlineStr">
+        <is>
+          <t>Roper (waiting)</t>
+        </is>
+      </c>
+      <c r="I50" s="36" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>04. Finance</t>
         </is>
       </c>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>Workday Company (GL) Creation</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C51" s="24" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="D49" s="25" t="n">
+      <c r="D51" s="25" t="n">
         <v>46077.70833332176</v>
       </c>
-      <c r="E49" s="25" t="n">
+      <c r="E51" s="25" t="n">
         <v>46077.70833332176</v>
       </c>
-      <c r="F49" s="26" t="inlineStr">
+      <c r="F51" s="26" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G49" s="26" t="n"/>
-      <c r="H49" s="26" t="n"/>
-      <c r="I49" s="26" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="G51" s="26" t="n"/>
+      <c r="H51" s="26" t="n"/>
+      <c r="I51" s="26" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>04. Finance</t>
         </is>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B52" s="23" t="inlineStr">
         <is>
           <t>GL Mapping</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C52" s="24" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="D50" s="25" t="n">
+      <c r="D52" s="25" t="n">
         <v>46084.70833332176</v>
       </c>
-      <c r="E50" s="25" t="n">
+      <c r="E52" s="25" t="n">
         <v>46084.70833332176</v>
       </c>
-      <c r="F50" s="26" t="inlineStr">
+      <c r="F52" s="26" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="G50" s="26" t="n"/>
-      <c r="H50" s="26" t="n"/>
-      <c r="I50" s="26" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="27" t="inlineStr">
-        <is>
-          <t>04. Finance</t>
-        </is>
-      </c>
-      <c r="B51" s="28" t="inlineStr">
-        <is>
-          <t>Closing balance sheet review and upload</t>
-        </is>
-      </c>
-      <c r="C51" s="29" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="n">
-        <v>46091.70833332176</v>
-      </c>
-      <c r="E51" s="30" t="n">
-        <v>46091.70833332176</v>
-      </c>
-      <c r="F51" s="31" t="inlineStr">
-        <is>
-          <t>OVERDUE — Roper needs to undo 2/17 QB reconciliation</t>
-        </is>
-      </c>
-      <c r="G51" s="31" t="inlineStr">
-        <is>
-          <t>Undo reconciliation in QB: Acct 1003 &gt; History &gt; Undo</t>
-        </is>
-      </c>
-      <c r="H51" s="31" t="inlineStr">
-        <is>
-          <t>Roper</t>
-        </is>
-      </c>
-      <c r="I51" s="31" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="27" t="inlineStr">
-        <is>
-          <t>04. Finance</t>
-        </is>
-      </c>
-      <c r="B52" s="28" t="inlineStr">
-        <is>
-          <t>Month end and finance &amp; accounting processes onboarding</t>
-        </is>
-      </c>
-      <c r="C52" s="29" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="D52" s="30" t="n">
-        <v>46085.33333333334</v>
-      </c>
-      <c r="E52" s="30" t="n">
-        <v>46126.70833332176</v>
-      </c>
-      <c r="F52" s="31" t="inlineStr">
-        <is>
-          <t>March close in progress</t>
-        </is>
-      </c>
-      <c r="G52" s="31" t="n"/>
-      <c r="H52" s="31" t="inlineStr">
-        <is>
-          <t>Mary Bamford</t>
-        </is>
-      </c>
-      <c r="I52" s="31" t="n"/>
+      <c r="G52" s="26" t="n"/>
+      <c r="H52" s="26" t="n"/>
+      <c r="I52" s="26" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="27" t="inlineStr">
@@ -2271,7 +2276,7 @@
       </c>
       <c r="B53" s="28" t="inlineStr">
         <is>
-          <t>Upload month 1 closing activity</t>
+          <t>Closing balance sheet review and upload</t>
         </is>
       </c>
       <c r="C53" s="29" t="inlineStr">
@@ -2280,42 +2285,64 @@
         </is>
       </c>
       <c r="D53" s="30" t="n">
-        <v>46106.70833332176</v>
+        <v>46091.70833332176</v>
       </c>
       <c r="E53" s="30" t="n">
-        <v>46106.70833332176</v>
+        <v>46091.70833332176</v>
       </c>
       <c r="F53" s="31" t="inlineStr">
         <is>
-          <t>Blocked by QB reconciliation undo</t>
-        </is>
-      </c>
-      <c r="G53" s="31" t="n"/>
+          <t>OVERDUE — Roper needs to undo 2/17 QB reconciliation</t>
+        </is>
+      </c>
+      <c r="G53" s="31" t="inlineStr">
+        <is>
+          <t>Undo reconciliation in QB: Acct 1003 &gt; History &gt; Undo</t>
+        </is>
+      </c>
       <c r="H53" s="31" t="inlineStr">
         <is>
-          <t>Roper → Mary Bamford</t>
-        </is>
-      </c>
-      <c r="I53" s="31" t="n"/>
+          <t>Roper</t>
+        </is>
+      </c>
+      <c r="I53" s="31" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>04. Finance</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>Upload month 2 closing activity</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="5" t="n">
-        <v>46134.70833332176</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>46134.70833332176</v>
-      </c>
+      <c r="B54" s="28" t="inlineStr">
+        <is>
+          <t>Month end and finance &amp; accounting processes onboarding</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="D54" s="30" t="n">
+        <v>46085.33333333334</v>
+      </c>
+      <c r="E54" s="30" t="n">
+        <v>46126.70833332176</v>
+      </c>
+      <c r="F54" s="31" t="inlineStr">
+        <is>
+          <t>March close in progress</t>
+        </is>
+      </c>
+      <c r="G54" s="31" t="n"/>
+      <c r="H54" s="31" t="inlineStr">
+        <is>
+          <t>Mary Bamford</t>
+        </is>
+      </c>
+      <c r="I54" s="31" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="27" t="inlineStr">
@@ -2325,38 +2352,32 @@
       </c>
       <c r="B55" s="28" t="inlineStr">
         <is>
-          <t>Coupa/ Accounts Payable Onboarding</t>
+          <t>Upload month 1 closing activity</t>
         </is>
       </c>
       <c r="C55" s="29" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D55" s="30" t="n">
-        <v>46133.70833332176</v>
+        <v>46106.70833332176</v>
       </c>
       <c r="E55" s="30" t="n">
-        <v>46133.70833332176</v>
+        <v>46106.70833332176</v>
       </c>
       <c r="F55" s="31" t="inlineStr">
         <is>
-          <t>Vendor list review needed. Target 4/21</t>
-        </is>
-      </c>
-      <c r="G55" s="31" t="inlineStr">
-        <is>
-          <t>Review QB vendors for Coupa</t>
-        </is>
-      </c>
+          <t>Blocked by QB reconciliation undo</t>
+        </is>
+      </c>
+      <c r="G55" s="31" t="n"/>
       <c r="H55" s="31" t="inlineStr">
         <is>
-          <t>Roper</t>
-        </is>
-      </c>
-      <c r="I55" s="31" t="n">
-        <v>7</v>
-      </c>
+          <t>Roper → Mary Bamford</t>
+        </is>
+      </c>
+      <c r="I55" s="31" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2366,157 +2387,197 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Opening balance sheet &amp; working capital true-up calculation</t>
+          <t>Upload month 2 closing activity</t>
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="5" t="n">
+        <v>46134.70833332176</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>46134.70833332176</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>04. Finance</t>
+        </is>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>Coupa/ Accounts Payable Onboarding</t>
+        </is>
+      </c>
+      <c r="C57" s="29" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D57" s="30" t="n">
+        <v>46133.70833332176</v>
+      </c>
+      <c r="E57" s="30" t="n">
+        <v>46133.70833332176</v>
+      </c>
+      <c r="F57" s="31" t="inlineStr">
+        <is>
+          <t>Vendor list review needed. Target 4/21</t>
+        </is>
+      </c>
+      <c r="G57" s="31" t="inlineStr">
+        <is>
+          <t>Review QB vendors for Coupa</t>
+        </is>
+      </c>
+      <c r="H57" s="31" t="inlineStr">
+        <is>
+          <t>Roper</t>
+        </is>
+      </c>
+      <c r="I57" s="31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>04. Finance</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Opening balance sheet &amp; working capital true-up calculation</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="5" t="n">
         <v>46175.70833332176</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E58" s="5" t="n">
         <v>46175.70833332176</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="22" t="inlineStr">
-        <is>
-          <t>05. Treasury</t>
-        </is>
-      </c>
-      <c r="B57" s="23" t="inlineStr">
-        <is>
-          <t>Banking Assessment</t>
-        </is>
-      </c>
-      <c r="C57" s="24" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="D57" s="32" t="n">
-        <v>46084.70833332176</v>
-      </c>
-      <c r="E57" s="25" t="n">
-        <v>46084.70833332176</v>
-      </c>
-      <c r="F57" s="26" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G57" s="26" t="n"/>
-      <c r="H57" s="26" t="n"/>
-      <c r="I57" s="26" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="22" t="inlineStr">
-        <is>
-          <t>05. Treasury</t>
-        </is>
-      </c>
-      <c r="B58" s="23" t="inlineStr">
-        <is>
-          <t>Creation of Wells Fargo Accounts (if needed)</t>
-        </is>
-      </c>
-      <c r="C58" s="24" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="n">
-        <v>46105.70833332176</v>
-      </c>
-      <c r="E58" s="25" t="n">
-        <v>46105.70833332176</v>
-      </c>
-      <c r="F58" s="26" t="inlineStr">
-        <is>
-          <t>Not needed per Keara recap</t>
-        </is>
-      </c>
-      <c r="G58" s="26" t="n"/>
-      <c r="H58" s="26" t="n"/>
-      <c r="I58" s="26" t="n"/>
-    </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>05. Treasury</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>Closing selected legacy bank accounts</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="16" t="n">
-        <v>46091.70833332176</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>46091.70833332176</v>
+      <c r="A59" s="36" t="inlineStr">
+        <is>
+          <t>04. Finance</t>
+        </is>
+      </c>
+      <c r="B59" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ AmEx statement — 3/20 payment for Mary Bamford</t>
+        </is>
+      </c>
+      <c r="C59" s="36" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ NEW 4/6 — Mary asked 4/6. Needs for March close (hard deadline today)</t>
+        </is>
+      </c>
+      <c r="G59" s="36" t="inlineStr">
+        <is>
+          <t>Locate and send AmEx statement to Mary</t>
+        </is>
+      </c>
+      <c r="H59" s="36" t="inlineStr">
+        <is>
+          <t>Roper</t>
+        </is>
+      </c>
+      <c r="I59" s="36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="inlineStr">
-        <is>
-          <t>05. Treasury</t>
-        </is>
-      </c>
-      <c r="B60" s="23" t="inlineStr">
-        <is>
-          <t>Addition of NFP signatory representative on legacy account (if applicable)</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="D60" s="25" t="n">
-        <v>46161.70833332176</v>
-      </c>
-      <c r="E60" s="25" t="n">
-        <v>46161.70833332176</v>
-      </c>
-      <c r="F60" s="26" t="inlineStr">
-        <is>
-          <t>Signers added to Landmark</t>
-        </is>
-      </c>
-      <c r="G60" s="26" t="n"/>
-      <c r="H60" s="26" t="n"/>
-      <c r="I60" s="26" t="n"/>
+      <c r="A60" s="36" t="inlineStr">
+        <is>
+          <t>04. Finance</t>
+        </is>
+      </c>
+      <c r="B60" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ Expense descriptions — Acumen KS $1,250 + OgleTree Deakins $170.10</t>
+        </is>
+      </c>
+      <c r="C60" s="36" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+      <c r="F60" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ NEW 4/6 — Mary asked 4/6. Invoices or statements needed</t>
+        </is>
+      </c>
+      <c r="G60" s="36" t="inlineStr">
+        <is>
+          <t>Provide descriptions + supporting docs to Mary</t>
+        </is>
+      </c>
+      <c r="H60" s="36" t="inlineStr">
+        <is>
+          <t>Roper</t>
+        </is>
+      </c>
+      <c r="I60" s="36" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>05. Treasury</t>
-        </is>
-      </c>
-      <c r="B61" s="15" t="inlineStr">
-        <is>
-          <t>Migration to Wells Fargo / NFP Banking Platform (TBC)</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="5" t="n">
-        <v>46168.70833332176</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>46168.70833332176</v>
+      <c r="A61" s="36" t="inlineStr">
+        <is>
+          <t>04. Finance</t>
+        </is>
+      </c>
+      <c r="B61" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ Deposit support — carrier statements for March</t>
+        </is>
+      </c>
+      <c r="C61" s="36" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D61" s="36" t="n"/>
+      <c r="E61" s="36" t="n"/>
+      <c r="F61" s="36" t="inlineStr">
+        <is>
+          <t>⬅️ NEW 4/6 — Mary asked 4/6. Less critical, by tomorrow</t>
+        </is>
+      </c>
+      <c r="G61" s="36" t="inlineStr">
+        <is>
+          <t>Email carrier statements to Mary</t>
+        </is>
+      </c>
+      <c r="H61" s="36" t="inlineStr">
+        <is>
+          <t>Roper</t>
+        </is>
+      </c>
+      <c r="I61" s="36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>07. Risk Management</t>
+          <t>05. Treasury</t>
         </is>
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Addition of coverage under NFP/Aon Insurance Program</t>
+          <t>Banking Assessment</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -2524,11 +2585,11 @@
           <t>Complete</t>
         </is>
       </c>
-      <c r="D62" s="25" t="n">
-        <v>46070.70833332176</v>
+      <c r="D62" s="32" t="n">
+        <v>46084.70833332176</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>46070.70833332176</v>
+        <v>46084.70833332176</v>
       </c>
       <c r="F62" s="26" t="inlineStr">
         <is>
@@ -2542,12 +2603,12 @@
     <row r="63">
       <c r="A63" s="22" t="inlineStr">
         <is>
-          <t>07. Risk Management</t>
+          <t>05. Treasury</t>
         </is>
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>Procurement of ERP's for E&amp;O</t>
+          <t>Creation of Wells Fargo Accounts (if needed)</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -2555,15 +2616,15 @@
           <t>Complete</t>
         </is>
       </c>
-      <c r="D63" s="25" t="n">
-        <v>46070.70833332176</v>
+      <c r="D63" s="32" t="n">
+        <v>46105.70833332176</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>46070.70833332176</v>
+        <v>46105.70833332176</v>
       </c>
       <c r="F63" s="26" t="inlineStr">
         <is>
-          <t>Paid KAIA, endorsement received</t>
+          <t>Not needed per Keara recap</t>
         </is>
       </c>
       <c r="G63" s="26" t="n"/>
@@ -2571,45 +2632,33 @@
       <c r="I63" s="26" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="inlineStr">
-        <is>
-          <t>08. Carrier Management</t>
-        </is>
-      </c>
-      <c r="B64" s="23" t="inlineStr">
-        <is>
-          <t>SIA communication with local contacts</t>
-        </is>
-      </c>
-      <c r="C64" s="24" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="D64" s="25" t="n">
-        <v>46072.70833332176</v>
-      </c>
-      <c r="E64" s="25" t="n">
-        <v>46072.70833332176</v>
-      </c>
-      <c r="F64" s="26" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G64" s="26" t="n"/>
-      <c r="H64" s="26" t="n"/>
-      <c r="I64" s="26" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>05. Treasury</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Closing selected legacy bank accounts</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="16" t="n">
+        <v>46091.70833332176</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>46091.70833332176</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="22" t="inlineStr">
         <is>
-          <t>08. Carrier Management</t>
+          <t>05. Treasury</t>
         </is>
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
-          <t>Initial Market Notification to NFP Contacts</t>
+          <t>Addition of NFP signatory representative on legacy account (if applicable)</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -2618,14 +2667,14 @@
         </is>
       </c>
       <c r="D65" s="25" t="n">
-        <v>46084.70833332176</v>
+        <v>46161.70833332176</v>
       </c>
       <c r="E65" s="25" t="n">
-        <v>46084.70833332176</v>
+        <v>46161.70833332176</v>
       </c>
       <c r="F65" s="26" t="inlineStr">
         <is>
-          <t>Sam Brown sent initial announcement</t>
+          <t>Signers added to Landmark</t>
         </is>
       </c>
       <c r="G65" s="26" t="n"/>
@@ -2633,74 +2682,64 @@
       <c r="I65" s="26" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="27" t="inlineStr">
-        <is>
-          <t>08. Carrier Management</t>
-        </is>
-      </c>
-      <c r="B66" s="28" t="inlineStr">
-        <is>
-          <t>Full Market Notification Initiation</t>
-        </is>
-      </c>
-      <c r="C66" s="29" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="D66" s="30" t="n">
-        <v>46126.70833332176</v>
-      </c>
-      <c r="E66" s="30" t="n">
-        <v>46126.70833332176</v>
-      </c>
-      <c r="F66" s="31" t="inlineStr">
-        <is>
-          <t>Sam Brown Step 2: needs address, contacts, role assignments. Target 4/14</t>
-        </is>
-      </c>
-      <c r="G66" s="31" t="inlineStr">
-        <is>
-          <t>Reply with address, phone, fax, contact roles, emails</t>
-        </is>
-      </c>
-      <c r="H66" s="31" t="inlineStr">
-        <is>
-          <t>Roper</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="n">
-        <v>9</v>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>05. Treasury</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>Migration to Wells Fargo / NFP Banking Platform (TBC)</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="5" t="n">
+        <v>46168.70833332176</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>46168.70833332176</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>08. Carrier Management</t>
-        </is>
-      </c>
-      <c r="B67" s="18" t="inlineStr">
-        <is>
-          <t>Ongoing Market Notification and consolidation</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="5" t="n">
-        <v>46127.33333333334</v>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>46154.70833332176</v>
-      </c>
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>07. Risk Management</t>
+        </is>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>Addition of coverage under NFP/Aon Insurance Program</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D67" s="25" t="n">
+        <v>46070.70833332176</v>
+      </c>
+      <c r="E67" s="25" t="n">
+        <v>46070.70833332176</v>
+      </c>
+      <c r="F67" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G67" s="26" t="n"/>
+      <c r="H67" s="26" t="n"/>
+      <c r="I67" s="26" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>09. Licensing &amp; Registrations</t>
+          <t>07. Risk Management</t>
         </is>
       </c>
       <c r="B68" s="23" t="inlineStr">
         <is>
-          <t>Change of Registered Agent to CT Corp. (Secretary of State)</t>
+          <t>Procurement of ERP's for E&amp;O</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -2709,14 +2748,14 @@
         </is>
       </c>
       <c r="D68" s="25" t="n">
-        <v>46084.70833332176</v>
+        <v>46070.70833332176</v>
       </c>
       <c r="E68" s="25" t="n">
-        <v>46084.70833332176</v>
+        <v>46070.70833332176</v>
       </c>
       <c r="F68" s="26" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Paid KAIA, endorsement received</t>
         </is>
       </c>
       <c r="G68" s="26" t="n"/>
@@ -2726,12 +2765,12 @@
     <row r="69">
       <c r="A69" s="22" t="inlineStr">
         <is>
-          <t>09. Licensing &amp; Registrations</t>
+          <t>08. Carrier Management</t>
         </is>
       </c>
       <c r="B69" s="23" t="inlineStr">
         <is>
-          <t>Introduction to Insurance Licensing</t>
+          <t>SIA communication with local contacts</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -2740,14 +2779,14 @@
         </is>
       </c>
       <c r="D69" s="25" t="n">
-        <v>46112.70833332176</v>
+        <v>46072.70833332176</v>
       </c>
       <c r="E69" s="25" t="n">
-        <v>46112.70833332176</v>
+        <v>46072.70833332176</v>
       </c>
       <c r="F69" s="26" t="inlineStr">
         <is>
-          <t>Lisa Black handling via RegEd</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G69" s="26" t="n"/>
@@ -2755,283 +2794,241 @@
       <c r="I69" s="26" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="27" t="inlineStr">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>08. Carrier Management</t>
+        </is>
+      </c>
+      <c r="B70" s="23" t="inlineStr">
+        <is>
+          <t>Initial Market Notification to NFP Contacts</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D70" s="25" t="n">
+        <v>46084.70833332176</v>
+      </c>
+      <c r="E70" s="25" t="n">
+        <v>46084.70833332176</v>
+      </c>
+      <c r="F70" s="26" t="inlineStr">
+        <is>
+          <t>Sam Brown sent initial announcement</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="n"/>
+      <c r="H70" s="26" t="n"/>
+      <c r="I70" s="26" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>08. Carrier Management</t>
+        </is>
+      </c>
+      <c r="B71" s="28" t="inlineStr">
+        <is>
+          <t>Full Market Notification Initiation</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="D71" s="30" t="n">
+        <v>46126.70833332176</v>
+      </c>
+      <c r="E71" s="30" t="n">
+        <v>46126.70833332176</v>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>Sam Brown Step 2: needs address, contacts, role assignments. Target 4/14</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>Reply with address, phone, fax, contact roles, emails</t>
+        </is>
+      </c>
+      <c r="H71" s="31" t="inlineStr">
+        <is>
+          <t>Roper</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>08. Carrier Management</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>Ongoing Market Notification and consolidation</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="5" t="n">
+        <v>46127.33333333334</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>46154.70833332176</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="inlineStr">
         <is>
           <t>09. Licensing &amp; Registrations</t>
         </is>
       </c>
-      <c r="B70" s="28" t="inlineStr">
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>Change of Registered Agent to CT Corp. (Secretary of State)</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D73" s="25" t="n">
+        <v>46084.70833332176</v>
+      </c>
+      <c r="E73" s="25" t="n">
+        <v>46084.70833332176</v>
+      </c>
+      <c r="F73" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G73" s="26" t="n"/>
+      <c r="H73" s="26" t="n"/>
+      <c r="I73" s="26" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>09. Licensing &amp; Registrations</t>
+        </is>
+      </c>
+      <c r="B74" s="23" t="inlineStr">
+        <is>
+          <t>Introduction to Insurance Licensing</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D74" s="25" t="n">
+        <v>46112.70833332176</v>
+      </c>
+      <c r="E74" s="25" t="n">
+        <v>46112.70833332176</v>
+      </c>
+      <c r="F74" s="26" t="inlineStr">
+        <is>
+          <t>Lisa Black handling via RegEd</t>
+        </is>
+      </c>
+      <c r="G74" s="26" t="n"/>
+      <c r="H74" s="26" t="n"/>
+      <c r="I74" s="26" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>09. Licensing &amp; Registrations</t>
+        </is>
+      </c>
+      <c r="B75" s="28" t="inlineStr">
         <is>
           <t>Initiation or Reged Process</t>
         </is>
       </c>
-      <c r="C70" s="29" t="inlineStr">
+      <c r="C75" s="29" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="D70" s="30" t="n">
+      <c r="D75" s="30" t="n">
         <v>46126.70833332176</v>
       </c>
-      <c r="E70" s="30" t="n">
+      <c r="E75" s="30" t="n">
         <v>46126.70833332176</v>
       </c>
-      <c r="F70" s="31" t="inlineStr">
+      <c r="F75" s="31" t="inlineStr">
         <is>
           <t>Personal licenses in RegEd. Agency licenses: ask RegEd to handle despite asset purchase</t>
         </is>
       </c>
-      <c r="G70" s="31" t="inlineStr">
+      <c r="G75" s="31" t="inlineStr">
         <is>
           <t>Ask RegEd about agency license renewals</t>
         </is>
       </c>
-      <c r="H70" s="31" t="inlineStr">
+      <c r="H75" s="31" t="inlineStr">
         <is>
           <t>Roper</t>
         </is>
       </c>
-      <c r="I70" s="31" t="n">
+      <c r="I75" s="31" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>10. Region/Sales/Ops</t>
         </is>
       </c>
-      <c r="B71" s="19" t="inlineStr">
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>Regional Sales Updates</t>
         </is>
       </c>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="5" t="n">
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="5" t="n">
         <v>46134.33333333334</v>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E76" s="5" t="n">
         <v>46161.70833332176</v>
       </c>
     </row>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" s="33" t="inlineStr">
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="33" t="inlineStr">
         <is>
           <t>ROPER'S ADDITIONAL ITEMS (added 4/5)</t>
         </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="34" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="B75" s="34" t="inlineStr">
-        <is>
-          <t>Send ranked list to Keara</t>
-        </is>
-      </c>
-      <c r="C75" s="34" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="D75" s="35" t="n">
-        <v>46117</v>
-      </c>
-      <c r="E75" s="34" t="n"/>
-      <c r="F75" s="34" t="inlineStr">
-        <is>
-          <t>This spreadsheet</t>
-        </is>
-      </c>
-      <c r="G75" s="34" t="inlineStr">
-        <is>
-          <t>Send to Keara</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>Roper</t>
-        </is>
-      </c>
-      <c r="I75" s="34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="34" t="inlineStr">
-        <is>
-          <t>Regional/Sales</t>
-        </is>
-      </c>
-      <c r="B76" s="34" t="inlineStr">
-        <is>
-          <t>Tess full-time conversation with Brett</t>
-        </is>
-      </c>
-      <c r="C76" s="34" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="D76" s="35" t="n">
-        <v>46117</v>
-      </c>
-      <c r="E76" s="34" t="n"/>
-      <c r="F76" s="34" t="inlineStr">
-        <is>
-          <t>Tess pursuing MA P&amp;C license (NFP reimburses)</t>
-        </is>
-      </c>
-      <c r="G76" s="34" t="inlineStr">
-        <is>
-          <t>Schedule conversation with Brett</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>Roper</t>
-        </is>
-      </c>
-      <c r="I76" s="34" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="34" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B77" s="34" t="inlineStr">
-        <is>
-          <t>AI Strategy deep dive + Gaya pilot</t>
-        </is>
-      </c>
-      <c r="C77" s="34" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="D77" s="35" t="n">
-        <v>46117</v>
-      </c>
-      <c r="E77" s="34" t="n"/>
-      <c r="F77" s="34" t="inlineStr">
-        <is>
-          <t>Mark Rieder + Katherine Minami</t>
-        </is>
-      </c>
-      <c r="G77" s="34" t="inlineStr">
-        <is>
-          <t>Confirm Mon 4/6 3pm CT invite</t>
-        </is>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>Roper</t>
-        </is>
-      </c>
-      <c r="I77" s="34" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="34" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B78" s="34" t="inlineStr">
-        <is>
-          <t>CanopyConnect credentials</t>
-        </is>
-      </c>
-      <c r="C78" s="34" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="D78" s="35" t="n">
-        <v>46117</v>
-      </c>
-      <c r="E78" s="34" t="n"/>
-      <c r="F78" s="34" t="inlineStr">
-        <is>
-          <t>Demo done with Josh Zacher</t>
-        </is>
-      </c>
-      <c r="G78" s="34" t="inlineStr">
-        <is>
-          <t>Get user ID and password</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>Josh Zacher → Roper</t>
-        </is>
-      </c>
-      <c r="I78" s="34" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="34" t="inlineStr">
-        <is>
-          <t>Regional/Sales</t>
-        </is>
-      </c>
-      <c r="B79" s="34" t="inlineStr">
-        <is>
-          <t>Goals in UltiPro</t>
-        </is>
-      </c>
-      <c r="C79" s="34" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="D79" s="35" t="n">
-        <v>46117</v>
-      </c>
-      <c r="E79" s="34" t="n"/>
-      <c r="F79" s="34" t="inlineStr">
-        <is>
-          <t>PCG retention 93.5%, PR retention 90%, growth 5.3%</t>
-        </is>
-      </c>
-      <c r="G79" s="34" t="inlineStr">
-        <is>
-          <t>Enter goals in UltiPro</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>Roper</t>
-        </is>
-      </c>
-      <c r="I79" s="34" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>Regional/Sales</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
         <is>
-          <t>NB premium goal for EPIC</t>
+          <t>Send ranked list to Keara</t>
         </is>
       </c>
       <c r="C80" s="34" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D80" s="35" t="n">
@@ -3040,12 +3037,12 @@
       <c r="E80" s="34" t="n"/>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>Mary Mullen asked 2/26</t>
+          <t>This spreadsheet</t>
         </is>
       </c>
       <c r="G80" s="34" t="inlineStr">
         <is>
-          <t>Clarify what Mary needs, provide goal</t>
+          <t>Send to Keara</t>
         </is>
       </c>
       <c r="H80" s="34" t="inlineStr">
@@ -3054,18 +3051,18 @@
         </is>
       </c>
       <c r="I80" s="34" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Regional/Sales</t>
         </is>
       </c>
       <c r="B81" s="34" t="inlineStr">
         <is>
-          <t>DNS/Registrar migration + domain admin</t>
+          <t>Tess full-time conversation with Brett</t>
         </is>
       </c>
       <c r="C81" s="34" t="inlineStr">
@@ -3079,32 +3076,32 @@
       <c r="E81" s="34" t="n"/>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>John Seckner: Hover to Brandsight. Tracy needs admin</t>
+          <t>Tess pursuing MA P&amp;C license (NFP reimburses)</t>
         </is>
       </c>
       <c r="G81" s="34" t="inlineStr">
         <is>
-          <t>Export DNS records (Excel), give admin access</t>
+          <t>Schedule conversation with Brett</t>
         </is>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
-          <t>Roper (waiting)</t>
+          <t>Roper</t>
         </is>
       </c>
       <c r="I81" s="34" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="34" t="inlineStr">
         <is>
-          <t>Regional/Sales</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
         <is>
-          <t>Life insurance policy list + commission</t>
+          <t>AI Strategy deep dive + Gaya pilot</t>
         </is>
       </c>
       <c r="C82" s="34" t="inlineStr">
@@ -3118,32 +3115,32 @@
       <c r="E82" s="34" t="n"/>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>Julie Lovall + Logan Christianson</t>
+          <t>Mark Rieder + Katherine Minami</t>
         </is>
       </c>
       <c r="G82" s="34" t="inlineStr">
         <is>
-          <t>Provide active life policy list</t>
+          <t>Confirm Mon 4/6 3pm CT invite</t>
         </is>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
-          <t>Roper (waiting)</t>
+          <t>Roper</t>
         </is>
       </c>
       <c r="I82" s="34" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="34" t="inlineStr">
         <is>
-          <t>Carrier Mgmt</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B83" s="34" t="inlineStr">
         <is>
-          <t>Berkley One code decision</t>
+          <t>CanopyConnect credentials</t>
         </is>
       </c>
       <c r="C83" s="34" t="inlineStr">
@@ -3157,32 +3154,32 @@
       <c r="E83" s="34" t="n"/>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>Roper prefers dedicated KC code. Not urgent</t>
+          <t>Demo done with Josh Zacher</t>
         </is>
       </c>
       <c r="G83" s="34" t="inlineStr">
         <is>
-          <t>Decide when Mary raises it</t>
+          <t>Get user ID and password</t>
         </is>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
-          <t>Roper (waiting)</t>
+          <t>Josh Zacher → Roper</t>
         </is>
       </c>
       <c r="I83" s="34" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Regional/Sales</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
         <is>
-          <t>Copilot license</t>
+          <t>Goals in UltiPro</t>
         </is>
       </c>
       <c r="C84" s="34" t="inlineStr">
@@ -3196,12 +3193,12 @@
       <c r="E84" s="34" t="n"/>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>ServiceNow REQ0412467</t>
+          <t>PCG retention 93.5%, PR retention 90%, growth 5.3%</t>
         </is>
       </c>
       <c r="G84" s="34" t="inlineStr">
         <is>
-          <t>Sign consent form, activate</t>
+          <t>Enter goals in UltiPro</t>
         </is>
       </c>
       <c r="H84" s="34" t="inlineStr">
@@ -3210,7 +3207,7 @@
         </is>
       </c>
       <c r="I84" s="34" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
@@ -3221,7 +3218,7 @@
       </c>
       <c r="B85" s="34" t="inlineStr">
         <is>
-          <t>P&amp;C Town Hall — April 20</t>
+          <t>NB premium goal for EPIC</t>
         </is>
       </c>
       <c r="C85" s="34" t="inlineStr">
@@ -3235,12 +3232,12 @@
       <c r="E85" s="34" t="n"/>
       <c r="F85" s="34" t="inlineStr">
         <is>
-          <t>Registration open</t>
+          <t>Mary Mullen asked 2/26</t>
         </is>
       </c>
       <c r="G85" s="34" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Clarify what Mary needs, provide goal</t>
         </is>
       </c>
       <c r="H85" s="34" t="inlineStr">
@@ -3249,194 +3246,222 @@
         </is>
       </c>
       <c r="I85" s="34" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="86"/>
-    <row r="87"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="34" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B86" s="34" t="inlineStr">
+        <is>
+          <t>DNS/Registrar migration + domain admin</t>
+        </is>
+      </c>
+      <c r="C86" s="34" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D86" s="35" t="n">
+        <v>46117</v>
+      </c>
+      <c r="E86" s="34" t="n"/>
+      <c r="F86" s="34" t="inlineStr">
+        <is>
+          <t>John Seckner: Hover to Brandsight. Tracy needs admin | Courtney follow-up 4/6: John needs DNS exports (Excel) for 4 domains this week</t>
+        </is>
+      </c>
+      <c r="G86" s="34" t="inlineStr">
+        <is>
+          <t>Export DNS records (Excel), give admin access</t>
+        </is>
+      </c>
+      <c r="H86" s="34" t="inlineStr">
+        <is>
+          <t>Roper (waiting)</t>
+        </is>
+      </c>
+      <c r="I86" s="34" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="34" t="inlineStr">
+        <is>
+          <t>Regional/Sales</t>
+        </is>
+      </c>
+      <c r="B87" s="34" t="inlineStr">
+        <is>
+          <t>Life insurance policy list + commission</t>
+        </is>
+      </c>
+      <c r="C87" s="34" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D87" s="35" t="n">
+        <v>46117</v>
+      </c>
+      <c r="E87" s="34" t="n"/>
+      <c r="F87" s="34" t="inlineStr">
+        <is>
+          <t>Julie Lovall + Logan Christianson</t>
+        </is>
+      </c>
+      <c r="G87" s="34" t="inlineStr">
+        <is>
+          <t>Provide active life policy list</t>
+        </is>
+      </c>
+      <c r="H87" s="34" t="inlineStr">
+        <is>
+          <t>Roper (waiting)</t>
+        </is>
+      </c>
+      <c r="I87" s="34" t="n">
+        <v>17</v>
+      </c>
+    </row>
     <row r="88">
-      <c r="A88" s="33" t="inlineStr">
-        <is>
-          <t>WAITING ON NFP (added 4/5)</t>
-        </is>
+      <c r="A88" s="34" t="inlineStr">
+        <is>
+          <t>Carrier Mgmt</t>
+        </is>
+      </c>
+      <c r="B88" s="34" t="inlineStr">
+        <is>
+          <t>Berkley One code decision</t>
+        </is>
+      </c>
+      <c r="C88" s="34" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D88" s="35" t="n">
+        <v>46117</v>
+      </c>
+      <c r="E88" s="34" t="n"/>
+      <c r="F88" s="34" t="inlineStr">
+        <is>
+          <t>Roper prefers dedicated KC code. Not urgent</t>
+        </is>
+      </c>
+      <c r="G88" s="34" t="inlineStr">
+        <is>
+          <t>Decide when Mary raises it</t>
+        </is>
+      </c>
+      <c r="H88" s="34" t="inlineStr">
+        <is>
+          <t>Roper (waiting)</t>
+        </is>
+      </c>
+      <c r="I88" s="34" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="34" t="inlineStr">
         <is>
-          <t>Regional/Sales</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B89" s="34" t="inlineStr">
         <is>
-          <t>Susan Clifford — ALT report / AI agent</t>
+          <t>Copilot license</t>
         </is>
       </c>
       <c r="C89" s="34" t="inlineStr">
         <is>
-          <t>Waiting</t>
-        </is>
-      </c>
-      <c r="D89" s="34" t="n"/>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D89" s="35" t="n">
+        <v>46117</v>
+      </c>
       <c r="E89" s="34" t="n"/>
       <c r="F89" s="34" t="inlineStr">
         <is>
-          <t>Susan owes Roper sample data</t>
+          <t>ServiceNow REQ0412467</t>
         </is>
       </c>
       <c r="G89" s="34" t="inlineStr">
         <is>
-          <t>Send sample data</t>
+          <t>Sign consent form, activate</t>
         </is>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
-          <t>Susan Clifford</t>
-        </is>
-      </c>
-      <c r="I89" s="34" t="n"/>
+          <t>Roper</t>
+        </is>
+      </c>
+      <c r="I89" s="34" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Regional/Sales</t>
         </is>
       </c>
       <c r="B90" s="34" t="inlineStr">
         <is>
-          <t>HSA accounts (Optum)</t>
+          <t>P&amp;C Town Hall — April 20</t>
         </is>
       </c>
       <c r="C90" s="34" t="inlineStr">
         <is>
-          <t>Waiting</t>
-        </is>
-      </c>
-      <c r="D90" s="34" t="n"/>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D90" s="35" t="n">
+        <v>46117</v>
+      </c>
       <c r="E90" s="34" t="n"/>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>Andria Griffin to open accounts</t>
+          <t>Registration open</t>
         </is>
       </c>
       <c r="G90" s="34" t="inlineStr">
         <is>
-          <t>Open Optum accounts, address on 4/6 paycheck</t>
+          <t>Register</t>
         </is>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
-          <t>Andria Griffin</t>
-        </is>
-      </c>
-      <c r="I90" s="34" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="34" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="B91" s="34" t="inlineStr">
-        <is>
-          <t>Epic smoke testing + go-live</t>
-        </is>
-      </c>
-      <c r="C91" s="34" t="inlineStr">
-        <is>
-          <t>Waiting</t>
-        </is>
-      </c>
-      <c r="D91" s="34" t="n"/>
-      <c r="E91" s="34" t="n"/>
-      <c r="F91" s="34" t="inlineStr">
-        <is>
-          <t>Starts 4/7, go-live ~4/8</t>
-        </is>
-      </c>
-      <c r="G91" s="34" t="inlineStr">
-        <is>
-          <t>Complete smoke testing</t>
-        </is>
-      </c>
-      <c r="H91" s="34" t="inlineStr">
-        <is>
-          <t>NFP Tech</t>
-        </is>
-      </c>
-      <c r="I91" s="34" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="34" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B92" s="34" t="inlineStr">
-        <is>
-          <t>Go-Green rebranding</t>
-        </is>
-      </c>
-      <c r="C92" s="34" t="inlineStr">
-        <is>
-          <t>Waiting</t>
-        </is>
-      </c>
-      <c r="D92" s="34" t="n"/>
-      <c r="E92" s="34" t="n"/>
-      <c r="F92" s="34" t="inlineStr">
-        <is>
-          <t>Target ~June</t>
-        </is>
-      </c>
-      <c r="G92" s="34" t="inlineStr"/>
-      <c r="H92" s="34" t="inlineStr">
-        <is>
-          <t>NFP Marketing</t>
-        </is>
-      </c>
-      <c r="I92" s="34" t="n"/>
-    </row>
+          <t>Roper</t>
+        </is>
+      </c>
+      <c r="I90" s="34" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91"/>
+    <row r="92"/>
     <row r="93">
-      <c r="A93" s="34" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B93" s="34" t="inlineStr">
-        <is>
-          <t>Business cards + collateral + signage</t>
-        </is>
-      </c>
-      <c r="C93" s="34" t="inlineStr">
-        <is>
-          <t>Waiting</t>
-        </is>
-      </c>
-      <c r="D93" s="34" t="n"/>
-      <c r="E93" s="34" t="n"/>
-      <c r="F93" s="34" t="inlineStr">
-        <is>
-          <t>Target ~June</t>
-        </is>
-      </c>
-      <c r="G93" s="34" t="inlineStr"/>
-      <c r="H93" s="34" t="inlineStr">
-        <is>
-          <t>NFP Marketing</t>
-        </is>
-      </c>
-      <c r="I93" s="34" t="n"/>
+      <c r="A93" s="33" t="inlineStr">
+        <is>
+          <t>WAITING ON NFP (added 4/5)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="34" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Regional/Sales</t>
         </is>
       </c>
       <c r="B94" s="34" t="inlineStr">
         <is>
-          <t>Website transition</t>
+          <t>Susan Clifford — ALT report / AI agent</t>
         </is>
       </c>
       <c r="C94" s="34" t="inlineStr">
@@ -3448,13 +3473,17 @@
       <c r="E94" s="34" t="n"/>
       <c r="F94" s="34" t="inlineStr">
         <is>
-          <t>Target ~June</t>
-        </is>
-      </c>
-      <c r="G94" s="34" t="inlineStr"/>
+          <t>Susan owes Roper sample data</t>
+        </is>
+      </c>
+      <c r="G94" s="34" t="inlineStr">
+        <is>
+          <t>Send sample data</t>
+        </is>
+      </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
-          <t>NFP Marketing</t>
+          <t>Susan Clifford</t>
         </is>
       </c>
       <c r="I94" s="34" t="n"/>
@@ -3462,12 +3491,12 @@
     <row r="95">
       <c r="A95" s="34" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B95" s="34" t="inlineStr">
         <is>
-          <t>Social media transition</t>
+          <t>HSA accounts (Optum)</t>
         </is>
       </c>
       <c r="C95" s="34" t="inlineStr">
@@ -3479,13 +3508,17 @@
       <c r="E95" s="34" t="n"/>
       <c r="F95" s="34" t="inlineStr">
         <is>
-          <t>Target ~June</t>
-        </is>
-      </c>
-      <c r="G95" s="34" t="inlineStr"/>
+          <t>Andria Griffin to open accounts</t>
+        </is>
+      </c>
+      <c r="G95" s="34" t="inlineStr">
+        <is>
+          <t>Open Optum accounts, address on 4/6 paycheck</t>
+        </is>
+      </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
-          <t>NFP Marketing</t>
+          <t>Andria Griffin</t>
         </is>
       </c>
       <c r="I95" s="34" t="n"/>
@@ -3498,7 +3531,7 @@
       </c>
       <c r="B96" s="34" t="inlineStr">
         <is>
-          <t>Email system migration to @nfp.com</t>
+          <t>Epic smoke testing + go-live</t>
         </is>
       </c>
       <c r="C96" s="34" t="inlineStr">
@@ -3510,10 +3543,14 @@
       <c r="E96" s="34" t="n"/>
       <c r="F96" s="34" t="inlineStr">
         <is>
-          <t>Full migration + hypercare, target ~June</t>
-        </is>
-      </c>
-      <c r="G96" s="34" t="inlineStr"/>
+          <t>Starts 4/7, go-live ~4/8</t>
+        </is>
+      </c>
+      <c r="G96" s="34" t="inlineStr">
+        <is>
+          <t>Complete smoke testing</t>
+        </is>
+      </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
           <t>NFP Tech</t>
@@ -3524,12 +3561,12 @@
     <row r="97">
       <c r="A97" s="34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B97" s="34" t="inlineStr">
         <is>
-          <t>Office integration (conduct)</t>
+          <t>Go-Green rebranding</t>
         </is>
       </c>
       <c r="C97" s="34" t="inlineStr">
@@ -3547,84 +3584,239 @@
       <c r="G97" s="34" t="inlineStr"/>
       <c r="H97" s="34" t="inlineStr">
         <is>
+          <t>NFP Marketing</t>
+        </is>
+      </c>
+      <c r="I97" s="34" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="34" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B98" s="34" t="inlineStr">
+        <is>
+          <t>Business cards + collateral + signage</t>
+        </is>
+      </c>
+      <c r="C98" s="34" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="D98" s="34" t="n"/>
+      <c r="E98" s="34" t="n"/>
+      <c r="F98" s="34" t="inlineStr">
+        <is>
+          <t>Target ~June</t>
+        </is>
+      </c>
+      <c r="G98" s="34" t="inlineStr"/>
+      <c r="H98" s="34" t="inlineStr">
+        <is>
+          <t>NFP Marketing</t>
+        </is>
+      </c>
+      <c r="I98" s="34" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="34" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B99" s="34" t="inlineStr">
+        <is>
+          <t>Website transition</t>
+        </is>
+      </c>
+      <c r="C99" s="34" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="D99" s="34" t="n"/>
+      <c r="E99" s="34" t="n"/>
+      <c r="F99" s="34" t="inlineStr">
+        <is>
+          <t>Target ~June</t>
+        </is>
+      </c>
+      <c r="G99" s="34" t="inlineStr"/>
+      <c r="H99" s="34" t="inlineStr">
+        <is>
+          <t>NFP Marketing</t>
+        </is>
+      </c>
+      <c r="I99" s="34" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="34" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B100" s="34" t="inlineStr">
+        <is>
+          <t>Social media transition</t>
+        </is>
+      </c>
+      <c r="C100" s="34" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="D100" s="34" t="n"/>
+      <c r="E100" s="34" t="n"/>
+      <c r="F100" s="34" t="inlineStr">
+        <is>
+          <t>Target ~June</t>
+        </is>
+      </c>
+      <c r="G100" s="34" t="inlineStr"/>
+      <c r="H100" s="34" t="inlineStr">
+        <is>
+          <t>NFP Marketing</t>
+        </is>
+      </c>
+      <c r="I100" s="34" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="34" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B101" s="34" t="inlineStr">
+        <is>
+          <t>Email system migration to @nfp.com</t>
+        </is>
+      </c>
+      <c r="C101" s="34" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="D101" s="34" t="n"/>
+      <c r="E101" s="34" t="n"/>
+      <c r="F101" s="34" t="inlineStr">
+        <is>
+          <t>Full migration + hypercare, target ~June</t>
+        </is>
+      </c>
+      <c r="G101" s="34" t="inlineStr"/>
+      <c r="H101" s="34" t="inlineStr">
+        <is>
           <t>NFP Tech</t>
         </is>
       </c>
-      <c r="I97" s="34" t="n"/>
-    </row>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" s="33" t="inlineStr">
+      <c r="I101" s="34" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="34" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B102" s="34" t="inlineStr">
+        <is>
+          <t>Office integration (conduct)</t>
+        </is>
+      </c>
+      <c r="C102" s="34" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="D102" s="34" t="n"/>
+      <c r="E102" s="34" t="n"/>
+      <c r="F102" s="34" t="inlineStr">
+        <is>
+          <t>Target ~June</t>
+        </is>
+      </c>
+      <c r="G102" s="34" t="inlineStr"/>
+      <c r="H102" s="34" t="inlineStr">
+        <is>
+          <t>NFP Tech</t>
+        </is>
+      </c>
+      <c r="I102" s="34" t="n"/>
+    </row>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="33" t="inlineStr">
         <is>
           <t>COLOR LEGEND</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="26" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="26" t="inlineStr">
         <is>
           <t>Dark Green</t>
         </is>
       </c>
-      <c r="B101" s="26" t="inlineStr">
+      <c r="B106" s="26" t="inlineStr">
         <is>
           <t>Keara's item — confirmed complete</t>
         </is>
       </c>
-      <c r="C101" s="26" t="n"/>
-      <c r="D101" s="26" t="n"/>
-      <c r="E101" s="26" t="n"/>
-      <c r="F101" s="26" t="n"/>
-      <c r="G101" s="26" t="n"/>
-      <c r="H101" s="26" t="n"/>
-      <c r="I101" s="26" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="31" t="inlineStr">
+      <c r="C106" s="26" t="n"/>
+      <c r="D106" s="26" t="n"/>
+      <c r="E106" s="26" t="n"/>
+      <c r="F106" s="26" t="n"/>
+      <c r="G106" s="26" t="n"/>
+      <c r="H106" s="26" t="n"/>
+      <c r="I106" s="26" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="31" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
       </c>
-      <c r="B102" s="31" t="inlineStr">
+      <c r="B107" s="31" t="inlineStr">
         <is>
           <t>Keara's item — Roper updated with notes/status</t>
         </is>
       </c>
-      <c r="C102" s="31" t="n"/>
-      <c r="D102" s="31" t="n"/>
-      <c r="E102" s="31" t="n"/>
-      <c r="F102" s="31" t="n"/>
-      <c r="G102" s="31" t="n"/>
-      <c r="H102" s="31" t="n"/>
-      <c r="I102" s="31" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="34" t="inlineStr">
+      <c r="C107" s="31" t="n"/>
+      <c r="D107" s="31" t="n"/>
+      <c r="E107" s="31" t="n"/>
+      <c r="F107" s="31" t="n"/>
+      <c r="G107" s="31" t="n"/>
+      <c r="H107" s="31" t="n"/>
+      <c r="I107" s="31" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="34" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="B103" s="34" t="inlineStr">
+      <c r="B108" s="34" t="inlineStr">
         <is>
           <t>Roper added — not in Keara's original</t>
         </is>
       </c>
-      <c r="C103" s="34" t="n"/>
-      <c r="D103" s="34" t="n"/>
-      <c r="E103" s="34" t="n"/>
-      <c r="F103" s="34" t="n"/>
-      <c r="G103" s="34" t="n"/>
-      <c r="H103" s="34" t="n"/>
-      <c r="I103" s="34" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="C108" s="34" t="n"/>
+      <c r="D108" s="34" t="n"/>
+      <c r="E108" s="34" t="n"/>
+      <c r="F108" s="34" t="n"/>
+      <c r="G108" s="34" t="n"/>
+      <c r="H108" s="34" t="n"/>
+      <c r="I108" s="34" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>No color</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Keara's original — no update from Roper</t>
         </is>
